--- a/generated_datasets/russia_languages_dataset_inventory.xlsx
+++ b/generated_datasets/russia_languages_dataset_inventory.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,70 +472,125 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>opus_error</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>opus_ru_parallel_pairs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>opus_ru_parallel_documents</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>opus_ru_parallel_corpora</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>opus_mono_pairs_or_segments</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>opus_mono_documents</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>opus_mono_corpora</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>opus_cached_from_previous_run</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>wiki_checked</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>wiki_articles</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>wiki_pages</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>wiki_source_url</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>hf_checked</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>hf_query_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>hf_query_successes</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>hf_dataset_count</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>hf_ru_parallel_candidates</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>hf_top_datasets</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>hf_downloads_sum</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>hf_size_categories</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>hf_source_url</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>parallel_with_russian_source</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>monolingual_source</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>checked_at_utc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>wiki_error</t>
         </is>
@@ -578,60 +633,101 @@
         </is>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>1337</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Mozilla-I10n (566); wikimedia (771)</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1639</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Mozilla-I10n (354); wikimedia (1285)</t>
         </is>
       </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2920</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11250</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://bxr.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>SaranaAbidueva/buryat-russian_parallel_corpus; SaranaAbidueva/buryat_monocorpus; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>490277</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>HTTP Error 429: Too Many Requests</t>
-        </is>
-      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -670,60 +766,101 @@
         </is>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>209</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Tatoeba (209); Ubuntu (0)</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>894</v>
       </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Tatoeba (886); Ubuntu (0); wikimedia (8)</t>
         </is>
       </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>1575</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>12603</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://xal.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>LilNomto/kalmyk_monocorpus; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>489569</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -756,42 +893,79 @@
       <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Maghrebi/Abaza; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>161335</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -830,60 +1004,101 @@
         </is>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>150</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Mozilla-I10n (5); wikimedia (145)</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1741</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Mozilla-I10n (2); Tatoeba (32); Ubuntu (0); wikimedia (1707)</t>
         </is>
       </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>647</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5071</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://ady.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>376897</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>HTTP Error 429: Too Many Requests</t>
-        </is>
-      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -922,60 +1137,101 @@
         </is>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>496</v>
       </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Mozilla-I10n (489); Tatoeba (3); wikimedia (4)</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>835</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Mozilla-I10n (391); Tatoeba (120); Ubuntu (0); wikimedia (324)</t>
         </is>
       </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7133</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://kbd.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>490104</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>HTTP Error 429: Too Many Requests</t>
-        </is>
-      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1014,60 +1270,101 @@
         </is>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>570</v>
       </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>QED (243); TED2020 (225); wikimedia (102)</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>776</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>QED (315); TED2020 (312); Ubuntu (0); wikimedia (149)</t>
         </is>
       </c>
-      <c r="O7" t="b">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
         <v>2559</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>17562</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>https://inh.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>parchiev/ingush-russian; parchiev/ingush_proverbs; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>488902</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1106,60 +1403,101 @@
         </is>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>3431</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>QED (371); Tatoeba (18); Ubuntu (0); wikimedia (3042)</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>5873</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>9</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>QED (2323); Tatoeba (66); Ubuntu (0); wikimedia (3484)</t>
         </is>
       </c>
-      <c r="O8" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>866897</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1894378</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>866899</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1894391</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>https://ce.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>NM-development/chechen_given_names_bessmertnybarak_v0; NM-development/chechen_given_names; NM-development/chechen_male_given_names; NM-development/chechen_female_given_names; wikimedia/wikipedia</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>427866</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1198,60 +1536,101 @@
         </is>
       </c>
       <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>2392</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>QED (132); Tatoeba (1437); wikimedia (823)</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>6463</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>18</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>QED (3318); Tatoeba (1746); wikimedia (1399)</t>
         </is>
       </c>
-      <c r="O9" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
         <v>4016</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>18797</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>https://av.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>volina092/avarCorpora; Burtinsaw/avar-turkish-parallel; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>518780</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1286,52 +1665,93 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>534</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Tatoeba (534)</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1737</v>
       </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Tatoeba (1737)</t>
         </is>
       </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Murtazali/bible-dargwa-russian; Murtazali/dargwa-monocorpus; Murtazali/dargwa_dictionary; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>148788</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1370,60 +1790,101 @@
         </is>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>78</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>wikimedia (78)</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>148</v>
       </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>wikimedia (148)</t>
         </is>
       </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1053</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16236</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>https://lbe.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>487592</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>HTTP Error 429: Too Many Requests</t>
-        </is>
-      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1462,60 +1923,101 @@
         </is>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>238</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Tatoeba (76); wikimedia (162)</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>552</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Tatoeba (261); wikimedia (291)</t>
         </is>
       </c>
-      <c r="O12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>4477</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>15250</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>https://lez.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>leks-forever/corpus_of_cnal_lezgian_to_russian; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>490254</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1550,44 +2052,85 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>mahesh27/archi_rutul_asr; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; AlidarAsvarov/dagestan-constitution</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>19453</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1622,44 +2165,85 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>zxc0zxc0zxc/nanai-language; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; cis-lmu/udhr-lid</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>19183</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1694,52 +2278,93 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>67</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Tatoeba (67)</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>116</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Tatoeba (116)</t>
         </is>
       </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>siberian-lang-lab/evenki-speech; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; espnet/mms_ulab_v2</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>20476</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1778,60 +2403,101 @@
         </is>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>3157412</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Mozilla-I10n (848); NLLB (2488850); Tatoeba (5); Ubuntu (0); WikiMatrix (104983); XLEnt (15982); wikimedia (546744)</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>4756787</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>19</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Mozilla-I10n (666); NLLB (3812400); QED (545); Tatoeba (442); Ubuntu (0); WikiMatrix (256537); XLEnt (26887); wikimedia (659310)</t>
         </is>
       </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
         <v>64296</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>185190</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>https://ba.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>fsicoli/common_voice_17_0; AigizK/bashkir-russian-parallel-corpora; BashkirNLPWorld/bashkir-lora-qlora-benchmark; BashkirNLPWorld/bashkir-web-corpus; DmitriyV/bashkir-russian-parallel-corpora-filtered</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>410796</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1870,60 +2536,101 @@
         </is>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>68</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Tatoeba (13); wikimedia (55)</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>547</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>8</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Tatoeba (323); wikimedia (224)</t>
         </is>
       </c>
-      <c r="O17" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
         <v>2917</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>17741</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>https://krc.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>491422</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1958,52 +2665,93 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Tatoeba (2)</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>166</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>6</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Tatoeba (166)</t>
         </is>
       </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1; cointegrated/panlex-meanings</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>154663</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2038,52 +2786,93 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>16</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Tatoeba (16)</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>426</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>7</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Tatoeba (426)</t>
         </is>
       </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ansarzeinulla/Nogai-Unified-Corpus-v1; ansarzeinulla/Nogai-Russian-SFT-Biblical-v1; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>144096</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2122,60 +2911,101 @@
         </is>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>1150452</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>229</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>GNOME (25769); Mozilla-I10n (1353); NLLB (739777); OpenSubtitles (104681); QED (1640); TED2020 (263); Tanzil (71043); Tatoeba (9480); Ubuntu (0); WikiMatrix (86062); XLEnt (17360); wikimedia (93024)</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>6817319</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>288</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>CCMatrix (272693); GNOME (28639); Mozilla-I10n (1555); NLLB (5807746); OpenSubtitles (165486); QED (1344); TED2020 (344); Tanzil (10656); Tatoeba (93299); Ubuntu (0); WikiMatrix (230550); XLEnt (29498); wikimedia (175509)</t>
         </is>
       </c>
-      <c r="O20" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
         <v>709016</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1460957</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>1460959</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>https://tt.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>tagay1n/sampled-tatar-dataset; AigizK/tatar-russian-parallel-corpora; yasalma/tatar-exams; saillab/alpaca_tatar_taco; saillab/alpaca-tatar-cleaned</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>449265</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2214,60 +3044,101 @@
         </is>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>814180</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>288</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>GNOME (155033); KDE4 (2813); Mozilla-I10n (9886); NLLB (646266); Tatoeba (36); Ubuntu (0); wikimedia (146)</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>974214</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>293</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>GNOME (217368); KDE4 (2796); Mozilla-I10n (8653); NLLB (743255); Tatoeba (769); Ubuntu (0); wikimedia (1373)</t>
         </is>
       </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
         <v>29723</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>58457</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>https://crh.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>gaydmi/CrimeanTatarMMLU-fork; wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; facebook/flores</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>385214</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2306,60 +3177,101 @@
         </is>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>1002013</v>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>ChuBiCo (1002013)</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>1257751</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>ChuBiCo (1257751)</t>
         </is>
       </c>
-      <c r="O22" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
         <v>59151</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>123583</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>https://cv.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>alexantonov/chuvash_mono; alexantonov/chuvash_llm_testset; rustemgareev/chuvash-names; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>146636</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2398,60 +3310,101 @@
         </is>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>175</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Tatoeba (77); wikimedia (98)</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1739</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>5</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Tatoeba (1587); wikimedia (152)</t>
         </is>
       </c>
-      <c r="O23" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
         <v>1111</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>7314</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>https://alt.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>375915</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2490,60 +3443,101 @@
         </is>
       </c>
       <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>12961</v>
       </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Tatoeba (12); wikimedia (12949)</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>13687</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>9</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Tatoeba (84); wikimedia (13603)</t>
         </is>
       </c>
-      <c r="O24" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
         <v>4124</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>15173</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://tyv.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>489544</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2578,44 +3572,85 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>adeshkin/khakas-russian-dict; adeshkin/khakas-russian-parallel-corpus; adeshkin/khakas-monolingual-corpus; adeshkin/russian-khakas-literary-dict; adeshkin/khakas-explanatory-dict</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>135195</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2654,60 +3689,101 @@
         </is>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
         <v>9989</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Mozilla-I10n (518); Tatoeba (996); wikimedia (8475)</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>12042</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>9</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Mozilla-I10n (608); Tatoeba (1025); wikimedia (10409)</t>
         </is>
       </c>
-      <c r="O26" t="b">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>18221</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>55395</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>18220</v>
+      </c>
+      <c r="S26" t="n">
+        <v>55399</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>https://sah.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>3</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; legacy-datasets/common_voice; fsicoli/common_voice_17_0</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>414687</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2746,60 +3822,101 @@
         </is>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>11</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>wikimedia (11)</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>141</v>
       </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>Tatoeba (95); wikimedia (46)</t>
         </is>
       </c>
-      <c r="O27" t="b">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
         <v>10430</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>21687</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>https://mrj.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>OneAdder/mari-bert-pretrain-hill-mari; OneAdder/hill-mari-book-corpus; OneAdder/hill-mari-msu-spoken-corpus; wikimedia/wikipedia; legacy-datasets/wikipedia</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>500207</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2838,60 +3955,101 @@
         </is>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
         <v>3805</v>
       </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Tatoeba (3786); Ubuntu (0); wikimedia (19)</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>4735</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>5</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Tatoeba (4557); Ubuntu (0); wikimedia (178)</t>
         </is>
       </c>
-      <c r="O28" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
         <v>11326</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>31824</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>https://mhr.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="b">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>OneAdder/meadow-mari-marnii-corpus; wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; fsicoli/common_voice_17_0</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>387125</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2930,60 +4088,101 @@
         </is>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>30</v>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Mozilla-I10n (30)</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>60</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>5</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Mozilla-I10n (19); Tatoeba (9); wikimedia (32)</t>
         </is>
       </c>
-      <c r="O29" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
         <v>7629</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>24112</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>https://mdf.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>catherinearnett/moksha; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>500720</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3022,60 +4221,101 @@
         </is>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
         <v>4353</v>
       </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Mozilla-I10n (634); Tatoeba (1); wikimedia (3718)</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>4647</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>8</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Mozilla-I10n (429); Tatoeba (382); wikimedia (3836)</t>
         </is>
       </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
         <v>7873</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>32026</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>https://myv.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>catherinearnett/erzya; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>499114</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3114,60 +4354,101 @@
         </is>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>708</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Mozilla-I10n (704); Tatoeba (4)</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>702</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>4</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Mozilla-I10n (613); Tatoeba (89)</t>
         </is>
       </c>
-      <c r="O31" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
         <v>5821</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>20285</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>https://kv.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cointegrated/panlex-meanings; ayymen/Pontoon-Translations; Helsinki-NLP/tatoeba</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>135719</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3206,60 +4487,101 @@
         </is>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>64</v>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>wikimedia (64)</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>189</v>
       </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Tatoeba (44); wikimedia (145)</t>
         </is>
       </c>
-      <c r="O32" t="b">
-        <v>1</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
         <v>3471</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>13973</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>https://koi.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>491147</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3298,60 +4620,101 @@
         </is>
       </c>
       <c r="H33" t="b">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>526</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Tatoeba (337); wikimedia (189)</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>5536</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>5</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Tatoeba (4975); Ubuntu (0); wikimedia (561)</t>
         </is>
       </c>
-      <c r="O33" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
         <v>5918</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>20502</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>https://udm.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>udmurtNLP/flores-250-rus-udm; udmurtNLP/udmurt-russian-english-labse; udmurtNLP/soviet-geography-book-rus-udm-parallel-corpora; udmurtNLP/udmurt-bible-parallel-corpora; udmurtNLP/zerpal</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>491576</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3390,60 +4753,101 @@
         </is>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
         <v>33</v>
       </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>Tatoeba (33)</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>526</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>6</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Tatoeba (436); wikimedia (90)</t>
         </is>
       </c>
-      <c r="O34" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
         <v>7112</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>39561</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>https://vep.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="b">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>catherinearnett/veps; Lynxpda/original-veps-russian; Lynxpda/back-translated-russian-veps; Lynxpda/back-translated-veps-russian; Lynxpda/dic-veps-russian</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>394860</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3482,48 +4886,89 @@
         </is>
       </c>
       <c r="H35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
         <is>
           <t>https://krl.wikipedia.org/</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="b">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>tartuNLP/smugri-flores-testset; catherinearnett/karelian; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; ayymen/Weblate-Translations</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>138312</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
         <is>
           <t>&lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
@@ -3562,44 +5007,85 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="b">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="b">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>shnyakov/nenets; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>154488</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3634,44 +5120,85 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>tartuNLP/smugri-data; tartuNLP/smugri-flores-testset; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>140364</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3704,42 +5231,79 @@
       <c r="H38" t="b">
         <v>0</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="b">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3</v>
+      </c>
+      <c r="X38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>tartuNLP/smugri-data; slone/finugorbib; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>142933</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3772,42 +5336,79 @@
       <c r="H39" t="b">
         <v>0</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr">
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="b">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3</v>
+      </c>
+      <c r="X39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>lblommesteyn/nivkh-cultural-heritage-corpus; utjktjdykydrysjt/NivkhGlossary; openbmb/DCAD-2000; jake-anto/wiktionary; cis-lmu/udhr-lid</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>15493</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3840,42 +5441,79 @@
       <c r="H40" t="b">
         <v>0</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="b">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" t="n">
+        <v>3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>openbmb/DCAD-2000; jake-anto/wiktionary; lbourdois/panlex; lbourdois/language_tags</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>14476</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3908,42 +5546,79 @@
       <c r="H41" t="b">
         <v>0</v>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>0</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr">
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="b">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>alexantonov/chukot_russian_flores_sample; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>154211</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3978,44 +5653,85 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="b">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>&lt;urlopen error timed out&gt;</t>
+        </is>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="b">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr">
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="b">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Tamazight-NLP/Weblate-Translations; cointegrated/panlex-meanings; gtak1/panlex-meanings; espnet/mms_ulab_v2; coml/mmsulab</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>9579</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4048,42 +5764,79 @@
       <c r="H43" t="b">
         <v>0</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="b">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr">
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="b">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; universal-dependencies/universal_dependencies; KefranAbg/finepdfs</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>151265</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>https://opus.nlpl.eu/opusapi</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics where available</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4131,7 +5884,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OPUS API; Wikipedia siteinfo statistics.</t>
+          <t>OPUS API; Wikipedia siteinfo statistics; Hugging Face dataset API.</t>
         </is>
       </c>
     </row>
@@ -4143,7 +5896,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/generated_datasets/russia_languages_dataset_inventory.xlsx
+++ b/generated_datasets/russia_languages_dataset_inventory.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG43"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,137 +462,107 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>wiki_code</t>
+          <t>opus_checked</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>opus_checked</t>
+          <t>opus_error</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>opus_error</t>
+          <t>opus_ru_parallel_pairs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>opus_ru_parallel_pairs</t>
+          <t>opus_ru_parallel_documents</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>opus_ru_parallel_documents</t>
+          <t>opus_ru_parallel_corpora</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>opus_ru_parallel_corpora</t>
+          <t>opus_mono_pairs_or_segments</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>opus_mono_pairs_or_segments</t>
+          <t>opus_mono_documents</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>opus_mono_documents</t>
+          <t>opus_mono_corpora</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>opus_mono_corpora</t>
+          <t>opus_cached_from_previous_run</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>opus_cached_from_previous_run</t>
+          <t>hf_checked</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>wiki_checked</t>
+          <t>hf_query_attempts</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>wiki_articles</t>
+          <t>hf_query_successes</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>wiki_pages</t>
+          <t>hf_dataset_count</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>wiki_source_url</t>
+          <t>hf_ru_parallel_candidates</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>hf_checked</t>
+          <t>hf_top_datasets</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>hf_query_attempts</t>
+          <t>hf_downloads_sum</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>hf_query_successes</t>
+          <t>hf_size_categories</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>hf_dataset_count</t>
+          <t>hf_source_url</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>hf_ru_parallel_candidates</t>
+          <t>parallel_with_russian_source</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>hf_top_datasets</t>
+          <t>monolingual_source</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>hf_downloads_sum</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>hf_size_categories</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>hf_source_url</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>parallel_with_russian_source</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>monolingual_source</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
           <t>checked_at_utc</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>wiki_error</t>
         </is>
       </c>
     </row>
@@ -627,107 +597,87 @@
           <t>bxr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>bxr</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I2" t="n">
+        <v>1337</v>
+      </c>
       <c r="J2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Mozilla-I10n (566); wikimedia (771)</t>
         </is>
       </c>
+      <c r="L2" t="n">
+        <v>1639</v>
+      </c>
       <c r="M2" t="n">
-        <v>1639</v>
-      </c>
-      <c r="N2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Mozilla-I10n (354); wikimedia (1285)</t>
         </is>
       </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" t="b">
-        <v>1</v>
+      <c r="Q2" t="n">
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>2920</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>11250</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>https://bxr.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U2" t="b">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SaranaAbidueva/buryat-russian_parallel_corpus; SaranaAbidueva/buryat_monocorpus; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
+        </is>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>9</v>
+        <v>490277</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>SaranaAbidueva/buryat-russian_parallel_corpus; SaranaAbidueva/buryat_monocorpus; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>490277</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -760,107 +710,87 @@
           <t>xal</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>xal</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I3" t="n">
+        <v>209</v>
+      </c>
       <c r="J3" t="n">
-        <v>209</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Tatoeba (209); Ubuntu (0)</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>894</v>
+      </c>
       <c r="M3" t="n">
-        <v>894</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tatoeba (886); Ubuntu (0); wikimedia (8)</t>
         </is>
       </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" t="b">
-        <v>1</v>
+      <c r="Q3" t="n">
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1575</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>12603</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>https://xal.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U3" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>LilNomto/kalmyk_monocorpus; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
+        <v>489569</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>LilNomto/kalmyk_monocorpus; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>489569</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -889,83 +819,75 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
       <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Maghrebi/Abaza; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
+        </is>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
+        <v>161335</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Maghrebi/Abaza; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>161335</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -998,107 +920,87 @@
           <t>ady</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ady</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>150</v>
+      </c>
       <c r="J5" t="n">
-        <v>150</v>
-      </c>
-      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Mozilla-I10n (5); wikimedia (145)</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>1741</v>
+      </c>
       <c r="M5" t="n">
-        <v>1741</v>
-      </c>
-      <c r="N5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Mozilla-I10n (2); Tatoeba (32); Ubuntu (0); wikimedia (1707)</t>
         </is>
       </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" t="b">
-        <v>1</v>
+      <c r="Q5" t="n">
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>647</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>5071</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>https://ady.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U5" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
+        </is>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8</v>
+        <v>376897</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>376897</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1131,107 +1033,87 @@
           <t>kbd</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>kbd</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>496</v>
+      </c>
       <c r="J6" t="n">
-        <v>496</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Mozilla-I10n (489); Tatoeba (3); wikimedia (4)</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>835</v>
+      </c>
       <c r="M6" t="n">
-        <v>835</v>
-      </c>
-      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Mozilla-I10n (391); Tatoeba (120); Ubuntu (0); wikimedia (324)</t>
         </is>
       </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" t="b">
-        <v>1</v>
+      <c r="Q6" t="n">
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1671</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>7133</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>https://kbd.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U6" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>8</v>
+        <v>490104</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>490104</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1264,107 +1146,87 @@
           <t>inh</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>inh</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>570</v>
+      </c>
       <c r="J7" t="n">
-        <v>570</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>QED (243); TED2020 (225); wikimedia (102)</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>776</v>
+      </c>
       <c r="M7" t="n">
-        <v>776</v>
-      </c>
-      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>QED (315); TED2020 (312); Ubuntu (0); wikimedia (149)</t>
         </is>
       </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" t="b">
-        <v>1</v>
+      <c r="Q7" t="n">
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>2559</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>17562</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>https://inh.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U7" t="b">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>parchiev/ingush-russian; parchiev/ingush_proverbs; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
+        </is>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10</v>
+        <v>488902</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>parchiev/ingush-russian; parchiev/ingush_proverbs; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
-        </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>488902</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1397,107 +1259,87 @@
           <t>ce</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ce</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>3431</v>
+      </c>
       <c r="J8" t="n">
-        <v>3431</v>
-      </c>
-      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>QED (371); Tatoeba (18); Ubuntu (0); wikimedia (3042)</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>5873</v>
+      </c>
       <c r="M8" t="n">
-        <v>5873</v>
-      </c>
-      <c r="N8" t="n">
         <v>9</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>QED (2323); Tatoeba (66); Ubuntu (0); wikimedia (3484)</t>
         </is>
       </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" t="b">
-        <v>1</v>
+      <c r="Q8" t="n">
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>866899</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>1894391</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>https://ce.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U8" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NM-development/chechen_given_names_bessmertnybarak_v0; NM-development/chechen_given_names; NM-development/chechen_male_given_names; NM-development/chechen_female_given_names; wikimedia/wikipedia</t>
+        </is>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12</v>
+        <v>427866</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>NM-development/chechen_given_names_bessmertnybarak_v0; NM-development/chechen_given_names; NM-development/chechen_male_given_names; NM-development/chechen_female_given_names; wikimedia/wikipedia</t>
-        </is>
-      </c>
-      <c r="AA8" t="n">
-        <v>427866</v>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1530,107 +1372,87 @@
           <t>av</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>av</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>2392</v>
+      </c>
       <c r="J9" t="n">
-        <v>2392</v>
-      </c>
-      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>QED (132); Tatoeba (1437); wikimedia (823)</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>6463</v>
+      </c>
       <c r="M9" t="n">
-        <v>6463</v>
-      </c>
-      <c r="N9" t="n">
         <v>18</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>QED (3318); Tatoeba (1746); wikimedia (1399)</t>
         </is>
       </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" t="b">
-        <v>1</v>
+      <c r="Q9" t="n">
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>4016</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>18797</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>https://av.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U9" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>volina092/avarCorpora; Burtinsaw/avar-turkish-parallel; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
+        </is>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12</v>
+        <v>518780</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>volina092/avarCorpora; Burtinsaw/avar-turkish-parallel; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2</t>
-        </is>
-      </c>
-      <c r="AA9" t="n">
-        <v>518780</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K; n&gt;1T</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1663,95 +1485,87 @@
           <t>dar</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>534</v>
+      </c>
       <c r="J10" t="n">
-        <v>534</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Tatoeba (534)</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>1737</v>
+      </c>
       <c r="M10" t="n">
-        <v>1737</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Tatoeba (1737)</t>
         </is>
       </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="b">
-        <v>1</v>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Murtazali/bible-dargwa-russian; Murtazali/dargwa-monocorpus; Murtazali/dargwa_dictionary; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>5</v>
+        <v>148788</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Murtazali/bible-dargwa-russian; Murtazali/dargwa-monocorpus; Murtazali/dargwa_dictionary; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA10" t="n">
-        <v>148788</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1784,107 +1598,87 @@
           <t>lbe</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>lbe</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>78</v>
+      </c>
       <c r="J11" t="n">
-        <v>78</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>wikimedia (78)</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>148</v>
+      </c>
       <c r="M11" t="n">
-        <v>148</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>wikimedia (148)</t>
         </is>
       </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
       <c r="P11" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="b">
-        <v>1</v>
+      <c r="Q11" t="n">
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1053</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>16236</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>https://lbe.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8</v>
+        <v>487592</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
-        </is>
-      </c>
-      <c r="AA11" t="n">
-        <v>487592</v>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1917,107 +1711,87 @@
           <t>lez</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>lez</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>238</v>
+      </c>
       <c r="J12" t="n">
-        <v>238</v>
-      </c>
-      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Tatoeba (76); wikimedia (162)</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>552</v>
+      </c>
       <c r="M12" t="n">
-        <v>552</v>
-      </c>
-      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Tatoeba (261); wikimedia (291)</t>
         </is>
       </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
       <c r="P12" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" t="b">
-        <v>1</v>
+      <c r="Q12" t="n">
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>4477</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>15250</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>https://lez.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U12" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>leks-forever/corpus_of_cnal_lezgian_to_russian; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9</v>
+        <v>490254</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>leks-forever/corpus_of_cnal_lezgian_to_russian; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA12" t="n">
-        <v>490254</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2050,87 +1824,79 @@
           <t>rut</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
       <c r="P13" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="b">
-        <v>1</v>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>mahesh27/archi_rutul_asr; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; AlidarAsvarov/dagestan-constitution</t>
+        </is>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2</v>
+        <v>19453</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>mahesh27/archi_rutul_asr; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; AlidarAsvarov/dagestan-constitution</t>
-        </is>
-      </c>
-      <c r="AA13" t="n">
-        <v>19453</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2163,87 +1929,79 @@
           <t>gld</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
       <c r="P14" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="b">
-        <v>1</v>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>zxc0zxc0zxc/nanai-language; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; cis-lmu/udhr-lid</t>
+        </is>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3</v>
+        <v>19183</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>zxc0zxc0zxc/nanai-language; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; cis-lmu/udhr-lid</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>19183</v>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2276,95 +2034,87 @@
           <t>evn</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>67</v>
+      </c>
       <c r="J15" t="n">
-        <v>67</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Tatoeba (67)</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>116</v>
+      </c>
       <c r="M15" t="n">
-        <v>116</v>
-      </c>
-      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Tatoeba (116)</t>
         </is>
       </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
       <c r="P15" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="b">
-        <v>1</v>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>siberian-lang-lab/evenki-speech; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; espnet/mms_ulab_v2</t>
+        </is>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
+        <v>20476</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>siberian-lang-lab/evenki-speech; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; espnet/mms_ulab_v2</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>20476</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1K&lt;n&lt;10K; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2397,107 +2147,87 @@
           <t>ba</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ba</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>3157412</v>
+      </c>
       <c r="J16" t="n">
-        <v>3157412</v>
-      </c>
-      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Mozilla-I10n (848); NLLB (2488850); Tatoeba (5); Ubuntu (0); WikiMatrix (104983); XLEnt (15982); wikimedia (546744)</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>4756787</v>
+      </c>
       <c r="M16" t="n">
-        <v>4756787</v>
-      </c>
-      <c r="N16" t="n">
         <v>19</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Mozilla-I10n (666); NLLB (3812400); QED (545); Tatoeba (442); Ubuntu (0); WikiMatrix (256537); XLEnt (26887); wikimedia (659310)</t>
         </is>
       </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
       <c r="P16" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" t="b">
-        <v>1</v>
+      <c r="Q16" t="n">
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>64296</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>185190</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>https://ba.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U16" t="b">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>fsicoli/common_voice_17_0; AigizK/bashkir-russian-parallel-corpora; BashkirNLPWorld/bashkir-lora-qlora-benchmark; BashkirNLPWorld/bashkir-web-corpus; DmitriyV/bashkir-russian-parallel-corpora-filtered</t>
+        </is>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>12</v>
+        <v>410796</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>fsicoli/common_voice_17_0; AigizK/bashkir-russian-parallel-corpora; BashkirNLPWorld/bashkir-lora-qlora-benchmark; BashkirNLPWorld/bashkir-web-corpus; DmitriyV/bashkir-russian-parallel-corpora-filtered</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>410796</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2530,107 +2260,87 @@
           <t>krc</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>krc</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>68</v>
+      </c>
       <c r="J17" t="n">
-        <v>68</v>
-      </c>
-      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Tatoeba (13); wikimedia (55)</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>547</v>
+      </c>
       <c r="M17" t="n">
-        <v>547</v>
-      </c>
-      <c r="N17" t="n">
         <v>8</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Tatoeba (323); wikimedia (224)</t>
         </is>
       </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
       <c r="P17" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" t="b">
-        <v>1</v>
+      <c r="Q17" t="n">
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2917</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>17741</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>https://krc.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U17" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>8</v>
+        <v>491422</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>491422</v>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2663,95 +2373,87 @@
           <t>kum</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tatoeba (2)</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>166</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tatoeba (166)</t>
+        </is>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Tatoeba (2)</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>166</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Tatoeba (166)</t>
-        </is>
-      </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="b">
-        <v>1</v>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1; cointegrated/panlex-meanings</t>
+        </is>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2</v>
+        <v>154663</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1; cointegrated/panlex-meanings</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>154663</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2784,95 +2486,87 @@
           <t>nog</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>16</v>
+      </c>
       <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Tatoeba (16)</t>
         </is>
       </c>
+      <c r="L19" t="n">
+        <v>426</v>
+      </c>
       <c r="M19" t="n">
-        <v>426</v>
-      </c>
-      <c r="N19" t="n">
         <v>7</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Tatoeba (426)</t>
         </is>
       </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="b">
-        <v>1</v>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>ansarzeinulla/Nogai-Unified-Corpus-v1; ansarzeinulla/Nogai-Russian-SFT-Biblical-v1; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
+        </is>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>3</v>
+        <v>144096</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>ansarzeinulla/Nogai-Unified-Corpus-v1; ansarzeinulla/Nogai-Russian-SFT-Biblical-v1; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>144096</v>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2905,107 +2599,87 @@
           <t>tt</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>tt</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I20" t="n">
+        <v>1150452</v>
+      </c>
       <c r="J20" t="n">
-        <v>1150452</v>
-      </c>
-      <c r="K20" t="n">
         <v>229</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>GNOME (25769); Mozilla-I10n (1353); NLLB (739777); OpenSubtitles (104681); QED (1640); TED2020 (263); Tanzil (71043); Tatoeba (9480); Ubuntu (0); WikiMatrix (86062); XLEnt (17360); wikimedia (93024)</t>
         </is>
       </c>
+      <c r="L20" t="n">
+        <v>6817319</v>
+      </c>
       <c r="M20" t="n">
-        <v>6817319</v>
-      </c>
-      <c r="N20" t="n">
         <v>288</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>CCMatrix (272693); GNOME (28639); Mozilla-I10n (1555); NLLB (5807746); OpenSubtitles (165486); QED (1344); TED2020 (344); Tanzil (10656); Tatoeba (93299); Ubuntu (0); WikiMatrix (230550); XLEnt (29498); wikimedia (175509)</t>
         </is>
       </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
       <c r="P20" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" t="b">
-        <v>1</v>
+      <c r="Q20" t="n">
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>709016</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>1460959</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>https://tt.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U20" t="b">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="T20" t="n">
+        <v>12</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>tagay1n/sampled-tatar-dataset; AigizK/tatar-russian-parallel-corpora; yasalma/tatar-exams; saillab/alpaca_tatar_taco; saillab/alpaca-tatar-cleaned</t>
+        </is>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>12</v>
+        <v>449265</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>tagay1n/sampled-tatar-dataset; AigizK/tatar-russian-parallel-corpora; yasalma/tatar-exams; saillab/alpaca_tatar_taco; saillab/alpaca-tatar-cleaned</t>
-        </is>
-      </c>
-      <c r="AA20" t="n">
-        <v>449265</v>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3038,107 +2712,87 @@
           <t>crh</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>crh</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v>814180</v>
+      </c>
       <c r="J21" t="n">
-        <v>814180</v>
-      </c>
-      <c r="K21" t="n">
         <v>288</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>GNOME (155033); KDE4 (2813); Mozilla-I10n (9886); NLLB (646266); Tatoeba (36); Ubuntu (0); wikimedia (146)</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>974214</v>
+      </c>
       <c r="M21" t="n">
-        <v>974214</v>
-      </c>
-      <c r="N21" t="n">
         <v>293</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>GNOME (217368); KDE4 (2796); Mozilla-I10n (8653); NLLB (743255); Tatoeba (769); Ubuntu (0); wikimedia (1373)</t>
         </is>
       </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
       <c r="P21" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" t="b">
-        <v>1</v>
+      <c r="Q21" t="n">
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>29723</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>58457</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>https://crh.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U21" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>gaydmi/CrimeanTatarMMLU-fork; wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; facebook/flores</t>
+        </is>
       </c>
       <c r="V21" t="n">
-        <v>3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>7</v>
+        <v>385214</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>gaydmi/CrimeanTatarMMLU-fork; wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; facebook/flores</t>
-        </is>
-      </c>
-      <c r="AA21" t="n">
-        <v>385214</v>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3171,107 +2825,87 @@
           <t>chv</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>cv</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I22" t="n">
+        <v>1002013</v>
+      </c>
       <c r="J22" t="n">
-        <v>1002013</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>ChuBiCo (1002013)</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>1257751</v>
+      </c>
       <c r="M22" t="n">
-        <v>1257751</v>
-      </c>
-      <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>ChuBiCo (1257751)</t>
         </is>
       </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
       <c r="P22" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" t="b">
-        <v>1</v>
+      <c r="Q22" t="n">
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>59151</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>123583</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>https://cv.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U22" t="b">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>alexantonov/chuvash_mono; alexantonov/chuvash_llm_testset; rustemgareev/chuvash-names; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
+        <v>146636</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>alexantonov/chuvash_mono; alexantonov/chuvash_llm_testset; rustemgareev/chuvash-names; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>146636</v>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3304,107 +2938,87 @@
           <t>alt</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>alt</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>175</v>
+      </c>
       <c r="J23" t="n">
-        <v>175</v>
-      </c>
-      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Tatoeba (77); wikimedia (98)</t>
         </is>
       </c>
+      <c r="L23" t="n">
+        <v>1739</v>
+      </c>
       <c r="M23" t="n">
-        <v>1739</v>
-      </c>
-      <c r="N23" t="n">
         <v>5</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Tatoeba (1587); wikimedia (152)</t>
         </is>
       </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" t="b">
-        <v>1</v>
+      <c r="Q23" t="n">
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1111</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>7314</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>https://alt.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U23" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
+        </is>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>7</v>
+        <v>375915</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
-        </is>
-      </c>
-      <c r="AA23" t="n">
-        <v>375915</v>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3437,107 +3051,87 @@
           <t>tyv</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>tyv</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I24" t="n">
+        <v>12961</v>
+      </c>
       <c r="J24" t="n">
-        <v>12961</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Tatoeba (12); wikimedia (12949)</t>
         </is>
       </c>
+      <c r="L24" t="n">
+        <v>13687</v>
+      </c>
       <c r="M24" t="n">
-        <v>13687</v>
-      </c>
-      <c r="N24" t="n">
         <v>9</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Tatoeba (84); wikimedia (13603)</t>
         </is>
       </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
       <c r="P24" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" t="b">
-        <v>1</v>
+      <c r="Q24" t="n">
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>4124</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>15173</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>https://tyv.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U24" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
       </c>
       <c r="V24" t="n">
-        <v>3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8</v>
+        <v>489544</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
-        </is>
-      </c>
-      <c r="AA24" t="n">
-        <v>489544</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3570,87 +3164,79 @@
           <t>kjh</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
       <c r="P25" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="b">
-        <v>1</v>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>adeshkin/khakas-russian-dict; adeshkin/khakas-russian-parallel-corpus; adeshkin/khakas-monolingual-corpus; adeshkin/russian-khakas-literary-dict; adeshkin/khakas-explanatory-dict</t>
+        </is>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>8</v>
+        <v>135195</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>adeshkin/khakas-russian-dict; adeshkin/khakas-russian-parallel-corpus; adeshkin/khakas-monolingual-corpus; adeshkin/russian-khakas-literary-dict; adeshkin/khakas-explanatory-dict</t>
-        </is>
-      </c>
-      <c r="AA25" t="n">
-        <v>135195</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3683,107 +3269,87 @@
           <t>sah</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>sah</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I26" t="n">
+        <v>9989</v>
+      </c>
       <c r="J26" t="n">
-        <v>9989</v>
-      </c>
-      <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Mozilla-I10n (518); Tatoeba (996); wikimedia (8475)</t>
         </is>
       </c>
+      <c r="L26" t="n">
+        <v>12042</v>
+      </c>
       <c r="M26" t="n">
-        <v>12042</v>
-      </c>
-      <c r="N26" t="n">
         <v>9</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Mozilla-I10n (608); Tatoeba (1025); wikimedia (10409)</t>
         </is>
       </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
       <c r="P26" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" t="b">
-        <v>1</v>
+      <c r="Q26" t="n">
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>18220</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>55399</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>https://sah.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U26" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; legacy-datasets/common_voice; fsicoli/common_voice_17_0</t>
+        </is>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>8</v>
+        <v>414687</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; legacy-datasets/common_voice; fsicoli/common_voice_17_0</t>
-        </is>
-      </c>
-      <c r="AA26" t="n">
-        <v>414687</v>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3816,107 +3382,87 @@
           <t>mrj</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>mrj</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>11</v>
+      </c>
       <c r="J27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>wikimedia (11)</t>
         </is>
       </c>
+      <c r="L27" t="n">
+        <v>141</v>
+      </c>
       <c r="M27" t="n">
-        <v>141</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Tatoeba (95); wikimedia (46)</t>
         </is>
       </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
       <c r="P27" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" t="b">
-        <v>1</v>
+      <c r="Q27" t="n">
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>10430</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>21687</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>https://mrj.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U27" t="b">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>OneAdder/mari-bert-pretrain-hill-mari; OneAdder/hill-mari-book-corpus; OneAdder/hill-mari-msu-spoken-corpus; wikimedia/wikipedia; legacy-datasets/wikipedia</t>
+        </is>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>8</v>
+        <v>500207</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>OneAdder/mari-bert-pretrain-hill-mari; OneAdder/hill-mari-book-corpus; OneAdder/hill-mari-msu-spoken-corpus; wikimedia/wikipedia; legacy-datasets/wikipedia</t>
-        </is>
-      </c>
-      <c r="AA27" t="n">
-        <v>500207</v>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3949,107 +3495,87 @@
           <t>mhr</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>mhr</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>3805</v>
+      </c>
       <c r="J28" t="n">
-        <v>3805</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Tatoeba (3786); Ubuntu (0); wikimedia (19)</t>
         </is>
       </c>
+      <c r="L28" t="n">
+        <v>4735</v>
+      </c>
       <c r="M28" t="n">
-        <v>4735</v>
-      </c>
-      <c r="N28" t="n">
         <v>5</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Tatoeba (4557); Ubuntu (0); wikimedia (178)</t>
         </is>
       </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
       <c r="P28" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" t="b">
-        <v>1</v>
+      <c r="Q28" t="n">
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>11326</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>31824</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>https://mhr.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U28" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>OneAdder/meadow-mari-marnii-corpus; wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; fsicoli/common_voice_17_0</t>
+        </is>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>8</v>
+        <v>387125</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>OneAdder/meadow-mari-marnii-corpus; wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; fsicoli/common_voice_17_0</t>
-        </is>
-      </c>
-      <c r="AA28" t="n">
-        <v>387125</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4082,107 +3608,87 @@
           <t>mdf</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>mdf</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v>30</v>
+      </c>
       <c r="J29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Mozilla-I10n (30)</t>
         </is>
       </c>
+      <c r="L29" t="n">
+        <v>60</v>
+      </c>
       <c r="M29" t="n">
-        <v>60</v>
-      </c>
-      <c r="N29" t="n">
         <v>5</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Mozilla-I10n (19); Tatoeba (9); wikimedia (32)</t>
         </is>
       </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
       <c r="P29" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" t="b">
-        <v>1</v>
+      <c r="Q29" t="n">
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>7629</v>
+        <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>24112</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>https://mdf.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U29" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>catherinearnett/moksha; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>8</v>
+        <v>500720</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>catherinearnett/moksha; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA29" t="n">
-        <v>500720</v>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4215,107 +3721,87 @@
           <t>myv</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>myv</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>4353</v>
+      </c>
       <c r="J30" t="n">
-        <v>4353</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Mozilla-I10n (634); Tatoeba (1); wikimedia (3718)</t>
         </is>
       </c>
+      <c r="L30" t="n">
+        <v>4647</v>
+      </c>
       <c r="M30" t="n">
-        <v>4647</v>
-      </c>
-      <c r="N30" t="n">
         <v>8</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Mozilla-I10n (429); Tatoeba (382); wikimedia (3836)</t>
         </is>
       </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
       <c r="P30" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" t="b">
-        <v>1</v>
+      <c r="Q30" t="n">
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>7873</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>32026</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>https://myv.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U30" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>catherinearnett/erzya; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
+        </is>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>8</v>
+        <v>499114</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>catherinearnett/erzya; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA30" t="n">
-        <v>499114</v>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4348,107 +3834,87 @@
           <t>kpv</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>kv</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v>708</v>
+      </c>
       <c r="J31" t="n">
-        <v>708</v>
-      </c>
-      <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Mozilla-I10n (704); Tatoeba (4)</t>
         </is>
       </c>
+      <c r="L31" t="n">
+        <v>702</v>
+      </c>
       <c r="M31" t="n">
-        <v>702</v>
-      </c>
-      <c r="N31" t="n">
         <v>4</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Mozilla-I10n (613); Tatoeba (89)</t>
         </is>
       </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
       <c r="P31" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" t="b">
-        <v>1</v>
+      <c r="Q31" t="n">
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>5821</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>20285</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>https://kv.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U31" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cointegrated/panlex-meanings; ayymen/Pontoon-Translations; Helsinki-NLP/tatoeba</t>
+        </is>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>3</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>4</v>
+        <v>135719</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cointegrated/panlex-meanings; ayymen/Pontoon-Translations; Helsinki-NLP/tatoeba</t>
-        </is>
-      </c>
-      <c r="AA31" t="n">
-        <v>135719</v>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4481,107 +3947,87 @@
           <t>koi</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>koi</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I32" t="n">
+        <v>64</v>
+      </c>
       <c r="J32" t="n">
-        <v>64</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>wikimedia (64)</t>
         </is>
       </c>
+      <c r="L32" t="n">
+        <v>189</v>
+      </c>
       <c r="M32" t="n">
-        <v>189</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3</v>
-      </c>
-      <c r="O32" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>Tatoeba (44); wikimedia (145)</t>
         </is>
       </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
       <c r="P32" t="b">
         <v>1</v>
       </c>
-      <c r="Q32" t="b">
-        <v>1</v>
+      <c r="Q32" t="n">
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>3471</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>13973</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>https://koi.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U32" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+        </is>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>8</v>
+        <v>491147</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
-        </is>
-      </c>
-      <c r="AA32" t="n">
-        <v>491147</v>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4614,107 +4060,87 @@
           <t>udm</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>udm</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I33" t="n">
+        <v>526</v>
+      </c>
       <c r="J33" t="n">
-        <v>526</v>
-      </c>
-      <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Tatoeba (337); wikimedia (189)</t>
         </is>
       </c>
+      <c r="L33" t="n">
+        <v>5536</v>
+      </c>
       <c r="M33" t="n">
-        <v>5536</v>
-      </c>
-      <c r="N33" t="n">
         <v>5</v>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Tatoeba (4975); Ubuntu (0); wikimedia (561)</t>
         </is>
       </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
       <c r="P33" t="b">
         <v>1</v>
       </c>
-      <c r="Q33" t="b">
-        <v>1</v>
+      <c r="Q33" t="n">
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>5918</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>20502</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>https://udm.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U33" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="T33" t="n">
+        <v>13</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>udmurtNLP/flores-250-rus-udm; udmurtNLP/udmurt-russian-english-labse; udmurtNLP/soviet-geography-book-rus-udm-parallel-corpora; udmurtNLP/udmurt-bible-parallel-corpora; udmurtNLP/zerpal</t>
+        </is>
       </c>
       <c r="V33" t="n">
-        <v>3</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>13</v>
+        <v>491576</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>udmurtNLP/flores-250-rus-udm; udmurtNLP/udmurt-russian-english-labse; udmurtNLP/soviet-geography-book-rus-udm-parallel-corpora; udmurtNLP/udmurt-bible-parallel-corpora; udmurtNLP/zerpal</t>
-        </is>
-      </c>
-      <c r="AA33" t="n">
-        <v>491576</v>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4747,107 +4173,87 @@
           <t>vep</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>vep</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I34" t="n">
+        <v>33</v>
+      </c>
       <c r="J34" t="n">
-        <v>33</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Tatoeba (33)</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>526</v>
+      </c>
       <c r="M34" t="n">
-        <v>526</v>
-      </c>
-      <c r="N34" t="n">
         <v>6</v>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Tatoeba (436); wikimedia (90)</t>
         </is>
       </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
       <c r="P34" t="b">
         <v>1</v>
       </c>
-      <c r="Q34" t="b">
-        <v>1</v>
+      <c r="Q34" t="n">
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>7112</v>
+        <v>3</v>
       </c>
       <c r="S34" t="n">
-        <v>39561</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>https://vep.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U34" t="b">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>12</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>catherinearnett/veps; Lynxpda/original-veps-russian; Lynxpda/back-translated-russian-veps; Lynxpda/back-translated-veps-russian; Lynxpda/dic-veps-russian</t>
+        </is>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3</v>
-      </c>
-      <c r="X34" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>12</v>
+        <v>394860</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>catherinearnett/veps; Lynxpda/original-veps-russian; Lynxpda/back-translated-russian-veps; Lynxpda/back-translated-veps-russian; Lynxpda/dic-veps-russian</t>
-        </is>
-      </c>
-      <c r="AA34" t="n">
-        <v>394860</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4880,97 +4286,77 @@
           <t>krl</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>krl</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
       <c r="P35" t="b">
         <v>1</v>
       </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>https://krl.wikipedia.org/</t>
-        </is>
-      </c>
-      <c r="U35" t="b">
-        <v>1</v>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>tartuNLP/smugri-flores-testset; catherinearnett/karelian; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; ayymen/Weblate-Translations</t>
+        </is>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
-      </c>
-      <c r="W35" t="n">
-        <v>3</v>
-      </c>
-      <c r="X35" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>6</v>
+        <v>138312</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>tartuNLP/smugri-flores-testset; catherinearnett/karelian; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; ayymen/Weblate-Translations</t>
-        </is>
-      </c>
-      <c r="AA35" t="n">
-        <v>138312</v>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
         <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>&lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -5005,87 +4391,79 @@
           <t>yrk</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
       <c r="P36" t="b">
         <v>1</v>
       </c>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="b">
-        <v>1</v>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>shnyakov/nenets; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
+        </is>
       </c>
       <c r="V36" t="n">
-        <v>3</v>
-      </c>
-      <c r="W36" t="n">
-        <v>3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>3</v>
+        <v>154488</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>shnyakov/nenets; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
-        </is>
-      </c>
-      <c r="AA36" t="n">
-        <v>154488</v>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5118,87 +4496,79 @@
           <t>mns</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
       <c r="P37" t="b">
         <v>1</v>
       </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="b">
-        <v>1</v>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>tartuNLP/smugri-data; tartuNLP/smugri-flores-testset; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
+        </is>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2</v>
+        <v>140364</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>tartuNLP/smugri-data; tartuNLP/smugri-flores-testset; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
-        </is>
-      </c>
-      <c r="AA37" t="n">
-        <v>140364</v>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5227,83 +4597,75 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
       <c r="P38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>tartuNLP/smugri-data; slone/finugorbib; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
+        </is>
       </c>
       <c r="V38" t="n">
-        <v>3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2</v>
+        <v>142933</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>tartuNLP/smugri-data; slone/finugorbib; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/GlotCC-V1</t>
-        </is>
-      </c>
-      <c r="AA38" t="n">
-        <v>142933</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5332,83 +4694,75 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
       <c r="P39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>lblommesteyn/nivkh-cultural-heritage-corpus; utjktjdykydrysjt/NivkhGlossary; openbmb/DCAD-2000; jake-anto/wiktionary; cis-lmu/udhr-lid</t>
+        </is>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>3</v>
+        <v>15493</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>lblommesteyn/nivkh-cultural-heritage-corpus; utjktjdykydrysjt/NivkhGlossary; openbmb/DCAD-2000; jake-anto/wiktionary; cis-lmu/udhr-lid</t>
-        </is>
-      </c>
-      <c r="AA39" t="n">
-        <v>15493</v>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5437,83 +4791,75 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
       <c r="P40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>openbmb/DCAD-2000; jake-anto/wiktionary; lbourdois/panlex; lbourdois/language_tags</t>
+        </is>
       </c>
       <c r="V40" t="n">
-        <v>3</v>
-      </c>
-      <c r="W40" t="n">
-        <v>3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1</v>
+        <v>14476</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>openbmb/DCAD-2000; jake-anto/wiktionary; lbourdois/panlex; lbourdois/language_tags</t>
-        </is>
-      </c>
-      <c r="AA40" t="n">
-        <v>14476</v>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5542,83 +4888,75 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
       <c r="P41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>alexantonov/chukot_russian_flores_sample; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
+        </is>
       </c>
       <c r="V41" t="n">
-        <v>3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3</v>
-      </c>
-      <c r="X41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>4</v>
+        <v>154211</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>alexantonov/chukot_russian_flores_sample; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; cis-lmu/GlotCC-V1</t>
-        </is>
-      </c>
-      <c r="AA41" t="n">
-        <v>154211</v>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; n&lt;1K</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5651,87 +4989,79 @@
           <t>ale</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>&lt;urlopen error timed out&gt;</t>
         </is>
       </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
       <c r="P42" t="b">
         <v>1</v>
       </c>
-      <c r="Q42" t="b">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="b">
-        <v>1</v>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Tamazight-NLP/Weblate-Translations; cointegrated/panlex-meanings; gtak1/panlex-meanings; espnet/mms_ulab_v2; coml/mmsulab</t>
+        </is>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
-      </c>
-      <c r="W42" t="n">
-        <v>3</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1</v>
+        <v>9579</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1M&lt;n&lt;10M</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Tamazight-NLP/Weblate-Translations; cointegrated/panlex-meanings; gtak1/panlex-meanings; espnet/mms_ulab_v2; coml/mmsulab</t>
-        </is>
-      </c>
-      <c r="AA42" t="n">
-        <v>9579</v>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1M&lt;n&lt;10M</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5760,83 +5090,75 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
       <c r="P43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="b">
-        <v>0</v>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; universal-dependencies/universal_dependencies; KefranAbg/finepdfs</t>
+        </is>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3</v>
-      </c>
-      <c r="X43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1</v>
+        <v>151265</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&gt;1T</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://opus.nlpl.eu/opusapi</t>
+        </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; openbmb/DCAD-2000; universal-dependencies/universal_dependencies; KefranAbg/finepdfs</t>
-        </is>
-      </c>
-      <c r="AA43" t="n">
-        <v>151265</v>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1M&lt;n&lt;10M; n&gt;1T</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/datasets</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>https://opus.nlpl.eu/opusapi</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>OPUS monolingual rows; Wikipedia statistics; Hugging Face dataset search</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
+          <t>OPUS monolingual rows; Hugging Face dataset search</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5884,7 +5206,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OPUS API; Wikipedia siteinfo statistics; Hugging Face dataset API.</t>
+          <t>OPUS API; Hugging Face dataset API.</t>
         </is>
       </c>
     </row>

--- a/generated_datasets/russia_languages_dataset_inventory.xlsx
+++ b/generated_datasets/russia_languages_dataset_inventory.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,26 @@
           <t>checked_at_utc</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>agent_decision</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>agent_confidence</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>agent_next_actions</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>agent_review_reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -678,6 +698,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -791,6 +831,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -888,6 +948,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1001,6 +1081,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1114,6 +1214,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1227,6 +1347,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1340,6 +1480,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1453,6 +1613,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1566,6 +1746,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1679,6 +1879,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1792,6 +2012,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1897,6 +2137,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2002,6 +2262,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2115,6 +2395,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2228,6 +2528,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2341,6 +2661,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2454,6 +2794,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2567,6 +2927,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2680,6 +3060,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2793,6 +3193,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2906,6 +3326,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3019,6 +3459,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3132,6 +3592,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3237,6 +3717,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3350,6 +3850,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3463,6 +3983,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3576,6 +4116,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3689,6 +4249,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3802,6 +4382,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>accept_with_spot_check</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3915,6 +4515,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4028,6 +4648,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4141,6 +4781,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4254,6 +4914,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4359,6 +5039,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4464,6 +5164,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4569,6 +5289,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4666,6 +5406,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4763,6 +5523,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4860,6 +5640,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4957,6 +5757,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5062,6 +5882,26 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5157,6 +5997,26 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>needs_human_review</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
         </is>
       </c>
     </row>
@@ -5171,7 +6031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5213,22 +6073,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>checked_at_utc</t>
+          <t>decision_policy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>Agent assigns accept_with_spot_check / needs_human_review / needs_discovery and next actions from OPUS/HF observations.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>checked_at_utc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>caveat</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Counts are API snapshots and need linguistic/community review before publication.</t>
         </is>

--- a/generated_datasets/russia_languages_dataset_inventory.xlsx
+++ b/generated_datasets/russia_languages_dataset_inventory.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE43"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,26 +565,6 @@
           <t>checked_at_utc</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>agent_decision</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>agent_confidence</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>agent_next_actions</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>agent_review_reason</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -671,7 +651,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>490277</v>
+        <v>493832</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -695,27 +675,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -804,11 +764,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>489569</v>
+        <v>492177</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -828,27 +788,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -921,7 +861,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>161335</v>
+        <v>167099</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -945,27 +885,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1046,15 +966,15 @@
         <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; graelo/wikipedia; Helsinki-NLP/tatoeba</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>376897</v>
+        <v>382532</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1078,27 +998,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1183,11 +1083,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+          <t>anzorq/kbd-ru; wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>490104</v>
+        <v>492734</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1211,27 +1111,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1200,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>488902</v>
+        <v>491696</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1344,27 +1224,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1453,11 +1313,11 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>427866</v>
+        <v>542752</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1477,27 +1337,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1426,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>518780</v>
+        <v>522377</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1610,27 +1450,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1531,7 @@
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1719,11 +1539,11 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>148788</v>
+        <v>168559</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1743,27 +1563,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1848,11 +1648,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; graelo/wikipedia</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>487592</v>
+        <v>491349</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1876,27 +1676,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1765,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>490254</v>
+        <v>493804</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2009,27 +1789,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2106,11 +1866,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>mahesh27/archi_rutul_asr; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; AlidarAsvarov/dagestan-constitution</t>
+          <t>mahesh27/archi_rutul_asr; openbmb/DCAD-2000; cointegrated/panlex-meanings; gtak1/panlex-meanings; jake-anto/wiktionary</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>19453</v>
+        <v>19476</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2134,27 +1894,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2235,7 +1975,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>19183</v>
+        <v>19137</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2259,27 +1999,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2088,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>20476</v>
+        <v>20466</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2392,27 +2112,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2201,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>410796</v>
+        <v>417248</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2525,27 +2225,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2310,15 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; graelo/wikipedia</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>491422</v>
+        <v>494028</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+          <t>100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2658,27 +2338,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2427,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>154663</v>
+        <v>160631</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2791,27 +2451,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2540,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>144096</v>
+        <v>150158</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2924,27 +2564,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3033,11 +2653,11 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>449265</v>
+        <v>472563</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M; n&lt;1K</t>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; 1K&lt;n&lt;10K; 1M&lt;n&lt;10M</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3057,27 +2677,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3166,7 +2766,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>385214</v>
+        <v>391317</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3190,27 +2790,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3299,7 +2879,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>146636</v>
+        <v>152549</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3323,27 +2903,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3424,15 +2984,15 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly; graelo/wikipedia</t>
+          <t>wikimedia/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cis-lmu/Glot500; graelo/wikipedia</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>375915</v>
+        <v>384503</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3456,27 +3016,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3561,11 +3101,11 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; graelo/wikipedia</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>489544</v>
+        <v>494380</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3589,27 +3129,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3202,7 @@
         <v>15</v>
       </c>
       <c r="T25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3690,7 +3210,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>135195</v>
+        <v>143532</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3714,27 +3234,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3823,11 +3323,11 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>414687</v>
+        <v>433329</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3847,27 +3347,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3956,11 +3436,11 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>500207</v>
+        <v>502999</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K; n&gt;1T</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3980,27 +3460,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4089,11 +3549,11 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>387125</v>
+        <v>394669</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>100B&lt;n&lt;1T; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B; n&lt;1K</t>
+          <t>100B&lt;n&lt;1T; 100K&lt;n&lt;1M; 100M&lt;n&lt;1B; 10K&lt;n&lt;100K; 10M&lt;n&lt;100M; 1B&lt;n&lt;10B</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -4113,27 +3573,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4222,7 +3662,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>500720</v>
+        <v>503672</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -4246,27 +3686,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4355,7 +3775,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>499114</v>
+        <v>504101</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -4379,27 +3799,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>accept_with_spot_check</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4484,11 +3884,11 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cointegrated/panlex-meanings; ayymen/Pontoon-Translations; Helsinki-NLP/tatoeba</t>
+          <t>HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; cointegrated/panlex-meanings; albertvillanova/universal_dependencies; ayymen/Pontoon-Translations</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>135719</v>
+        <v>142402</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4512,27 +3912,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4617,11 +3997,11 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; omarkamali/wikipedia-monthly</t>
+          <t>wikimedia/wikipedia; legacy-datasets/wikipedia; HuggingFaceFW/fineweb-2; HuggingFaceFW/finepdfs; graelo/wikipedia</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>491147</v>
+        <v>493949</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4645,27 +4025,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4750,11 +4110,11 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>udmurtNLP/flores-250-rus-udm; udmurtNLP/udmurt-russian-english-labse; udmurtNLP/soviet-geography-book-rus-udm-parallel-corpora; udmurtNLP/udmurt-bible-parallel-corpora; udmurtNLP/zerpal</t>
+          <t>udmurtNLP/flores-250-rus-udm; udmurtNLP/udmurt-russian-english-labse; udmurtNLP/soviet-geography-book-rus-udm-parallel-corpora; udmurtNLP/udmurt-bible-parallel-corpora; udmurtNLP/tatoeba-rus-udm-parallel-corpora</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>491576</v>
+        <v>496765</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4778,27 +4138,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4883,11 +4223,11 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>catherinearnett/veps; Lynxpda/original-veps-russian; Lynxpda/back-translated-russian-veps; Lynxpda/back-translated-veps-russian; Lynxpda/dic-veps-russian</t>
+          <t>catherinearnett/veps; Lynxpda/back-translated-russian-veps; Lynxpda/original-veps-russian; Lynxpda/dic-veps-russian; Lynxpda/back-translated-veps-russian</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>394860</v>
+        <v>509686</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4911,27 +4251,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>retry_opus_later; accept_opus_parallel_stats; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5012,7 +4332,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>138312</v>
+        <v>144897</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -5036,27 +4356,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5137,7 +4437,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>154488</v>
+        <v>160534</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -5161,27 +4461,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5262,7 +4542,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>140364</v>
+        <v>146440</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -5286,27 +4566,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5379,7 +4639,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>142933</v>
+        <v>149023</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -5403,27 +4663,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5496,7 +4736,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>15493</v>
+        <v>15540</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5520,27 +4760,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5613,7 +4833,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>14476</v>
+        <v>14548</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5637,27 +4857,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5730,7 +4930,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>154211</v>
+        <v>160836</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5754,27 +4954,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5035,7 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>9579</v>
+        <v>9455</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5879,27 +5059,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>retry_opus_later; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>OPUS не ответил: статистика могла быть взята из кеша или остаться нулевой; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5132,7 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>151265</v>
+        <v>156829</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5996,27 +5156,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>needs_human_review</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>review_language_code_mapping; search_parallel_candidates; inspect_hf_parallel_cards</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>нет OPUS-кода: агент не может корректно проверить OPUS; OPUS не нашел русско-параллельные пары</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -6031,7 +5171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6073,34 +5213,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>decision_policy</t>
+          <t>checked_at_utc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agent assigns accept_with_spot_check / needs_human_review / needs_discovery and next actions from OPUS/HF observations.</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>checked_at_utc</t>
+          <t>caveat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>caveat</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
         <is>
           <t>Counts are API snapshots and need linguistic/community review before publication.</t>
         </is>
